--- a/HX_PMS/HX_PMS_Framework/src/test/resources/testdata/GuestData.xlsx
+++ b/HX_PMS/HX_PMS_Framework/src/test/resources/testdata/GuestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="WalkIn_Guest"/>
@@ -727,7 +727,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>15</v>
@@ -944,7 +944,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>15</v>
